--- a/official_program/000_official_program_仕様書.xlsx
+++ b/official_program/000_official_program_仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\競輪AI\official_program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549349F1-9D32-48DF-9993-6A105ECD3DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101D0344-D59B-4B3A-AB3E-A434D800F37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="0" windowWidth="13620" windowHeight="10170" xr2:uid="{ED16066A-6E59-4F8F-AEF4-5C969C934B6F}"/>
+    <workbookView xWindow="0" yWindow="510" windowWidth="13620" windowHeight="8900" xr2:uid="{ED16066A-6E59-4F8F-AEF4-5C969C934B6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
